--- a/ECU_WB_timeseries.xlsx
+++ b/ECU_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net inflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -440,12 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -513,8 +516,11 @@
       <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -534,31 +540,34 @@
         <v>126000000</v>
       </c>
       <c r="H2">
+        <v>15239272611.5809</v>
+      </c>
+      <c r="I2">
         <v>3.67991405308877</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1455.00748510871</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>12.3019782138532</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>21.8305402720974</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>48.5191129963729</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>1009075807.30826</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>3.22560194131569</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>44.5949122940278</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -578,34 +587,37 @@
         <v>160000000</v>
       </c>
       <c r="H3">
+        <v>16988535267.6338</v>
+      </c>
+      <c r="I3">
         <v>4.29134246404705</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1587.36049996672</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>11.3385886406281</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>21.5220563955058</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>48.718080675219</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>1080977277.89412</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>3.04786826473906</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>45.196639984556</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>4.385</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -625,34 +637,37 @@
         <v>178000000</v>
       </c>
       <c r="H4">
+        <v>18094238119.0595</v>
+      </c>
+      <c r="I4">
         <v>2.11431064978969</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1655.44613192632</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>9.938838909691359</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>20.6728035108946</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>54.6078215093597</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>1015827333.20143</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>3.05129611975399</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>44.8065436522069</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>4.346</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -672,34 +687,37 @@
         <v>473720000</v>
       </c>
       <c r="H5">
+        <v>18938717358.6793</v>
+      </c>
+      <c r="I5">
         <v>1.97321813678619</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1697.88884141445</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>10.6039500354161</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>23.1353775913338</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>44.9550537592163</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>1541717569.37448</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>3.76972639464956</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>43.1712184234683</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>4.415</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -719,37 +737,40 @@
         <v>576330000</v>
       </c>
       <c r="H6">
+        <v>22708673336.6683</v>
+      </c>
+      <c r="I6">
         <v>4.25825042741626</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>1996.85894789444</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>53.3</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>10.9567918572233</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>23.4979294250568</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>27.3108817940496</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>2002942790.09083</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>4.07814348584502</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>43.7777474951998</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>4.419</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -769,37 +790,40 @@
         <v>452480000</v>
       </c>
       <c r="H7">
+        <v>24432884442.2211</v>
+      </c>
+      <c r="I7">
         <v>2.25254865225104</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>2108.00698245316</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>50.8</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>11.2136981674703</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>24.624367359648</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>22.9341344145802</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>1787782198.96368</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>3.18466294477139</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>45.9112707318244</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>4.417</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -822,37 +846,40 @@
         <v>499680000</v>
       </c>
       <c r="H8">
+        <v>25226393196.5983</v>
+      </c>
+      <c r="I8">
         <v>1.73174762607862</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>2135.8479374308</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>10.8754339888743</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>21.9424179952391</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>24.4114592150674</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>-0.770033240318298</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>2011360128.31461</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>3.86842180554537</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>44.2157026832153</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>4.43</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -872,34 +899,37 @@
         <v>723950000</v>
       </c>
       <c r="H9">
+        <v>28162053026.5133</v>
+      </c>
+      <c r="I9">
         <v>4.32786475767577</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>2340.76600026857</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>11.2693127590151</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>23.4822601074067</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>30.6575675722173</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>2212962682.55717</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>3.66152168748946</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>45.0171863180765</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>4.431</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -922,40 +952,43 @@
         <v>869980000</v>
       </c>
       <c r="H10">
+        <v>27981896948.4742</v>
+      </c>
+      <c r="I10">
         <v>3.26652934570988</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>2284.01572847769</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>49.6</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>11.0929970945984</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>25.5031570829793</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>36.0984331623885</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>-0.162388324737549</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>1738909755.15919</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>2.61186126200329</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>43.395107949805</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>4.395</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -975,37 +1008,40 @@
         <v>648410000</v>
       </c>
       <c r="H11">
+        <v>19645272636.3182</v>
+      </c>
+      <c r="I11">
         <v>-4.73938585363382</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1575.30234730971</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>58.6</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>11.7675327023318</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>22.82370915869</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>52.2420051858225</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>1887630504.49257</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>4.05102074263774</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>49.2012507989376</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>4.658</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1028,40 +1064,43 @@
         <v>-23439367.9139981</v>
       </c>
       <c r="H12">
+        <v>17539454727.3637</v>
+      </c>
+      <c r="I12">
         <v>1.09180164720277</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>1382.23421759909</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>56.3</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>9.526923791055509</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>27.8532356265599</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>96.0963756926097</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>-0.572284936904907</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>1178958455.54319</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>2.20964916732945</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>65.40429538263911</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>4.8</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1081,34 +1120,37 @@
         <v>538568575.17</v>
       </c>
       <c r="H13">
+        <v>23127055000</v>
+      </c>
+      <c r="I13">
         <v>4.20627185748789</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>1791.30359685037</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>9.79192984147787</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>28.5213530213856</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>37.6767454518094</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>1073533298.23222</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>1.60557375051738</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>56.128486744205</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>4.252</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1131,37 +1173,40 @@
         <v>783261009.55</v>
       </c>
       <c r="H14">
+        <v>27054197000</v>
+      </c>
+      <c r="I14">
         <v>4.92809549611376</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>2059.1585535974</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>10.2548968649855</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>29.0822270570441</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>12.4835980082095</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>-0.759720921516418</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>1004402765.69838</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>1.32521230423304</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>54.7966439366136</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>4.836</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1184,40 +1229,43 @@
         <v>871513414.0236191</v>
       </c>
       <c r="H15">
+        <v>30965208000</v>
+      </c>
+      <c r="I15">
         <v>2.88450036512064</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>2315.62215223014</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>53.5</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>11.0932566640599</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>25.51576918198</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>7.92936487461556</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>-0.961056590080261</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>1165340428.48352</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>1.46494734190132</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>52.3575426975979</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>5.662</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1240,40 +1288,43 @@
         <v>836939593.8956439</v>
       </c>
       <c r="H16">
+        <v>35194947000</v>
+      </c>
+      <c r="I16">
         <v>6.83239736646514</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>2586.20914663347</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>53.9</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>11.2444976831475</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>26.9748580669833</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>2.74323198926705</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>-0.842910349369049</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>1439913954.63566</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>1.49066224423451</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>56.0745467239942</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>5.002</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1296,40 +1347,43 @@
         <v>493413835.545644</v>
       </c>
       <c r="H17">
+        <v>40278849000</v>
+      </c>
+      <c r="I17">
         <v>5.39862243994342</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>2909.02606014388</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>53.1</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>11.0374603802606</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>29.3310019856824</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>2.16827701183721</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>-0.793961822986603</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>2147944603.19674</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>1.8570146073896</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>61.9581507902572</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>3.779</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1352,40 +1406,43 @@
         <v>271428852.53</v>
       </c>
       <c r="H18">
+        <v>45690762000</v>
+      </c>
+      <c r="I18">
         <v>4.34113198577639</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>3243.67010359339</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>52.3</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>10.8776036608888</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>30.1406704488754</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>3.29874846258216</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>-0.853825330734253</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>2026480313.69129</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>1.53297404578316</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>65.84235561665621</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>3.55</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1408,40 +1465,43 @@
         <v>193872526.929999</v>
       </c>
       <c r="H19">
+        <v>49848725000</v>
+      </c>
+      <c r="I19">
         <v>1.90242859700484</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>3478.92488770671</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>53.4</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>11.1822498970636</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>31.3681523449196</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>2.27618478002121</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>-0.815987229347229</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>3520672992.45779</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>2.35703438208118</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>68.8505854462677</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>3.142</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1464,40 +1524,43 @@
         <v>1057404020.15481</v>
       </c>
       <c r="H20">
+        <v>61139438000</v>
+      </c>
+      <c r="I20">
         <v>6.56492068224719</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>4194.75750661981</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>49.8</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>12.0058038479189</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>34.3139954933835</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>8.400095939874619</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>-0.728682398796082</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>4472854631.28031</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>2.36581172716712</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>74.59029636484389</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>3.917</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1520,40 +1583,43 @@
         <v>308629890.109</v>
       </c>
       <c r="H21">
+        <v>60094978000</v>
+      </c>
+      <c r="I21">
         <v>1.0910129698311</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>4053.36331139298</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>48.5</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>14.3981565314825</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>28.0377172282183</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>5.15996829181047</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>-0.673675775527954</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>3792122231.6349</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>2.47902376115675</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>57.3473460627608</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>4.608</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1576,40 +1642,43 @@
         <v>165893320.363638</v>
       </c>
       <c r="H22">
+        <v>68151329000</v>
+      </c>
+      <c r="I22">
         <v>4.02913787986621</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>4520.30959039763</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>48.8</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>13.6565759414611</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>33.2916897335927</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>3.55437734567847</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>-0.586674451828003</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>2622493356.38252</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>1.32503175460345</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>65.7773849135062</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>4.088</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1632,40 +1701,43 @@
         <v>646084358.687903</v>
       </c>
       <c r="H23">
+        <v>78986648000</v>
+      </c>
+      <c r="I23">
         <v>8.481476563328229</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>5153.6916424375</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>45.9</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>13.0638269394594</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>33.9223143131735</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>4.47453265795836</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>-0.686557531356812</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>2957999383.64451</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>1.27331707779755</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>70.0356837525249</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>3.458</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1688,40 +1760,43 @@
         <v>567417300.85638</v>
       </c>
       <c r="H24">
+        <v>87735048000</v>
+      </c>
+      <c r="I24">
         <v>5.783212336172</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>5634.08393191094</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>46.1</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>13.7469463742699</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>32.1715182739742</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>5.10172180958668</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>-0.570306479930878</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>2486036143.68357</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>1.02501259645838</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>67.00292909168979</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>3.235</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -1744,55 +1819,58 @@
         <v>727081206.263418</v>
       </c>
       <c r="H25">
+        <v>96570334000</v>
+      </c>
+      <c r="I25">
         <v>7.21123653679159</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>6109.29031510341</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>46.9</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>14.2480971433732</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>33.5309774702576</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>30.5658423371221</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>31.058033826413</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>2.72177577710365</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>2.36439108722504</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>-7.53236226665665</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>-0.178656712174416</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>14.1232339142175</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>4345840333.46757</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>1.6795739912293</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>63.4333003342414</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>3.083</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -1815,55 +1893,58 @@
         <v>772389946.091118</v>
       </c>
       <c r="H26">
+        <v>102717794000</v>
+      </c>
+      <c r="I26">
         <v>4.22606520388456</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>6405.79979300441</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>45</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>14.7396467646102</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>33.3268796672496</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>28.8901339676781</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>30.0713399277247</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>3.58922016616669</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>2.5285013419883</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>-8.69249897895714</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>-0.0185332093387842</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>14.0206757250712</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>3941357097.57337</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>1.48540361456181</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>61.4263766217565</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>3.48</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -1886,55 +1967,58 @@
         <v>1322701337.30747</v>
       </c>
       <c r="H27">
+        <v>97209558000</v>
+      </c>
+      <c r="I27">
         <v>0.119692109287612</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>5976.1596805651</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>46</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>15.3738143732739</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>34.0758538247243</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>30.8458833789351</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>25.0735539811836</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>3.96664623255353</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>3.44256160173059</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>-5.69774311670289</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>-0.147344976663589</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>16.3890534868359</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>2487276599.56405</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>1.15848913221995</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>47.8280397077826</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>3.616</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -1957,55 +2041,58 @@
         <v>766570868.122241</v>
       </c>
       <c r="H28">
+        <v>97671433000</v>
+      </c>
+      <c r="I28">
         <v>-0.687954245877947</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>5917.63771271481</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>45</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>15.6897053000134</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>35.0549572104551</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>28.6412079584013</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>19.9952006437747</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>1.72826463324535</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>5.67008228171477</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>-8.57164995739415</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>-0.0917104333639145</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>14.5417706457609</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>4215553160.05677</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>2.32976739205994</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>40.5344917996647</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>4.597</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2028,55 +2115,58 @@
         <v>632393412.259199</v>
       </c>
       <c r="H29">
+        <v>104467486000</v>
+      </c>
+      <c r="I29">
         <v>5.97039880954841</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>6233.32244797718</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>44.7</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>15.2975347755569</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>31.5192679680287</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>27.9863154861129</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>22.1321359260048</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>0.41733558866682</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>5.72540950394934</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>-6.36519719285874</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>-0.0789320766925812</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>13.6893043126773</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>2169697856.6482</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>1.01291491040231</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>43.6177233172817</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>3.836</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2099,55 +2189,58 @@
         <v>1390916763.14022</v>
       </c>
       <c r="H30">
+        <v>107478961000</v>
+      </c>
+      <c r="I30">
         <v>1.04429460679607</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>6303.91886658338</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>45.4</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>15.5567599876593</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>33.7250449206698</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>31.2062328120813</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>24.4654774807509</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>-0.224103246005501</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>6.54590879626623</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>-3.52514850564392</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>-0.0947211682796478</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>14.2925485653785</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>2158694032.4143</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>0.870883341513735</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>48.0093476154836</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>3.53</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2170,55 +2263,58 @@
         <v>979633496.243027</v>
       </c>
       <c r="H31">
+        <v>107595830000</v>
+      </c>
+      <c r="I31">
         <v>0.1654044646003</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>6205.05765246766</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>45.7</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>15.184077301137</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>33.1468964953936</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>29.6599984642663</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>24.0342148947594</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>0.266012515466146</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>7.50314765724407</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>-4.27034595652833</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>-0.238217756152153</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>13.4008895884716</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>2939049266.08469</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>1.19546250045385</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>48.0828494933307</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>3.812</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2241,55 +2337,58 @@
         <v>1118946900.76401</v>
       </c>
       <c r="H32">
+        <v>95865473000</v>
+      </c>
+      <c r="I32">
         <v>-9.24509619165865</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>5463.64515348598</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>47.3</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>16.3225877996763</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>34.0396754166882</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>27.1210867326524</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>20.7057487735965</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>-0.338872392562181</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>8.102103348542149</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>-7.49141811316719</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>-0.270243227481842</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>12.9414345922817</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>7136589071.47075</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>3.62387628565021</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>43.9893109378389</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>6.127</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:24">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2312,55 +2411,58 @@
         <v>649918150.926888</v>
       </c>
       <c r="H33">
+        <v>107179074000</v>
+      </c>
+      <c r="I33">
         <v>9.42189269033631</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>6061.32350181711</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>45.8</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>14.4433893877456</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>31.9261749303125</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>29.6714820409688</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>26.1953000265705</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>0.133251386096379</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>3.66201297742773</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>-2.90457512420842</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>-0.25738736987114</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>12.73586840639</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>7912190379.51528</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>3.14068023207363</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>53.261275610573</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>4.552</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:24">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2383,55 +2485,58 @@
         <v>882020803.5295171</v>
       </c>
       <c r="H34">
+        <v>116133121000</v>
+      </c>
+      <c r="I34">
         <v>5.86842354862311</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>6515.58528418336</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>45.5</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>13.5357543693328</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>30.4365983203311</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>30.9625405355437</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>30.9555471259573</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>3.46616972213076</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>4.74391645927243</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>-0.00621626745664098</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>-0.37122431397438</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>13.0891981784206</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>8459270681.86545</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>2.61861331521052</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>61.880792818786</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>3.761</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2454,40 +2559,43 @@
         <v>481024348.523188</v>
       </c>
       <c r="H35">
+        <v>121147057000</v>
+      </c>
+      <c r="I35">
         <v>1.98823813984235</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>6737.84748379638</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>44.6</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>13.5836201122079</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>28.4318239773666</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>2.21568764237062</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>-0.338139981031418</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>4441563798.69096</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>1.38332314099579</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>56.9977535649091</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>3.51</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2501,33 +2609,36 @@
         <v>317695171.69482</v>
       </c>
       <c r="H36">
+        <v>124676074700</v>
+      </c>
+      <c r="I36">
         <v>-2.00125476341026</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>6874.705739766</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>45.2</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>13.2902251212758</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>26.9245388746587</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>1.54732515615369</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <v>6907743954.50087</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>2.19828678215529</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>57.2031395531255</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>4.773</v>
       </c>
     </row>

--- a/ECU_WB_timeseries.xlsx
+++ b/ECU_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F943BAAE-E3BB-704C-820C-2AD4B5C8C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,83 +472,74 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>-0.79962956905365001</v>
+        <v>-0.79962956905365</v>
       </c>
       <c r="C2">
-        <v>6.3435541480245003</v>
+        <v>6.3435541480245</v>
       </c>
       <c r="D2">
-        <v>37.551059756079098</v>
+        <v>37.5510597560791</v>
       </c>
       <c r="E2">
-        <v>1.0918016472027701</v>
+        <v>1.09180164720277</v>
       </c>
       <c r="F2">
         <v>1382.23421759909</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
       <c r="I2">
-        <v>27.853235626559901</v>
+        <v>27.8532356265599</v>
       </c>
       <c r="J2">
-        <v>96.096375692609698</v>
-      </c>
-      <c r="K2" s="2"/>
+        <v>96.0963756926097</v>
+      </c>
       <c r="L2">
         <v>-0.3</v>
       </c>
       <c r="M2">
         <v>-0.572284936904907</v>
       </c>
-      <c r="N2" s="2"/>
       <c r="O2">
-        <v>65.404295382639106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>65.40429538263911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
-        <v>-2.3832508825500498</v>
+        <v>-2.38325088255005</v>
       </c>
       <c r="D3">
-        <v>27.607133722819398</v>
+        <v>27.6071337228194</v>
       </c>
       <c r="E3">
-        <v>4.2062718574878897</v>
+        <v>4.20627185748789</v>
       </c>
       <c r="F3">
         <v>1791.30359685037</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
       <c r="I3">
         <v>28.5213530213856</v>
       </c>
       <c r="J3">
-        <v>37.676745451809403</v>
-      </c>
-      <c r="K3" s="2"/>
+        <v>37.6767454518094</v>
+      </c>
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="N3" s="2"/>
       <c r="O3">
-        <v>56.128486744204999</v>
+        <v>56.128486744205</v>
       </c>
       <c r="P3">
         <v>63.8</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -579,75 +547,67 @@
         <v>-0.86826103925705</v>
       </c>
       <c r="C4">
-        <v>-4.5058623449173503</v>
+        <v>-4.50586234491735</v>
       </c>
       <c r="D4">
-        <v>25.714416879569601</v>
+        <v>25.7144168795696</v>
       </c>
       <c r="E4">
-        <v>4.9280954961137597</v>
+        <v>4.92809549611376</v>
       </c>
       <c r="F4">
         <v>2059.1585535974</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
       <c r="I4">
-        <v>29.082227057044101</v>
+        <v>29.0822270570441</v>
       </c>
       <c r="J4">
-        <v>12.483598008209499</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>12.4835980082095</v>
+      </c>
       <c r="L4">
         <v>0.7</v>
       </c>
       <c r="M4">
-        <v>-0.75972092151641801</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>-0.759720921516418</v>
+      </c>
       <c r="O4">
-        <v>54.796643936613599</v>
+        <v>54.7966439366136</v>
       </c>
       <c r="P4">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>-0.72812420129776001</v>
+        <v>-0.72812420129776</v>
       </c>
       <c r="C5">
-        <v>-1.2492036168512901</v>
+        <v>-1.24920361685129</v>
       </c>
       <c r="D5">
-        <v>26.841773515617898</v>
+        <v>26.8417735156179</v>
       </c>
       <c r="E5">
         <v>2.88450036512064</v>
       </c>
       <c r="F5">
-        <v>2315.6221522301398</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+        <v>2315.62215223014</v>
+      </c>
       <c r="I5">
-        <v>25.515769181980001</v>
+        <v>25.51576918198</v>
       </c>
       <c r="J5">
-        <v>7.9293648746155601</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>7.92936487461556</v>
+      </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>-0.96105659008026101</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>-0.961056590080261</v>
+      </c>
       <c r="O5">
         <v>52.3575426975979</v>
       </c>
@@ -655,141 +615,129 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>-0.72666990756988503</v>
+        <v>-0.726669907569885</v>
       </c>
       <c r="C6">
-        <v>-1.3621918956077399</v>
+        <v>-1.36219189560774</v>
       </c>
       <c r="D6">
-        <v>29.099688657010901</v>
+        <v>29.0996886570109</v>
       </c>
       <c r="E6">
-        <v>6.8323973664651403</v>
+        <v>6.83239736646514</v>
       </c>
       <c r="F6">
         <v>2586.20914663347</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
       <c r="I6">
-        <v>26.974858066983298</v>
+        <v>26.9748580669833</v>
       </c>
       <c r="J6">
-        <v>2.7432319892670498</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>2.74323198926705</v>
+      </c>
       <c r="L6">
         <v>1.9</v>
       </c>
       <c r="M6">
-        <v>-0.84291034936904896</v>
-      </c>
-      <c r="N6" s="2"/>
+        <v>-0.842910349369049</v>
+      </c>
       <c r="O6">
-        <v>56.074546723994203</v>
+        <v>56.0745467239942</v>
       </c>
       <c r="P6">
-        <v>40.200000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>-0.73587894439697299</v>
+        <v>-0.735878944396973</v>
       </c>
       <c r="C7">
         <v>1.17661120468016</v>
       </c>
       <c r="D7">
-        <v>32.627148804574801</v>
+        <v>32.6271488045748</v>
       </c>
       <c r="E7">
-        <v>5.3986224399434199</v>
+        <v>5.39862243994342</v>
       </c>
       <c r="F7">
-        <v>2909.0260601438799</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+        <v>2909.02606014388</v>
+      </c>
       <c r="I7">
-        <v>29.331001985682398</v>
+        <v>29.3310019856824</v>
       </c>
       <c r="J7">
-        <v>2.1682770118372101</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>2.16827701183721</v>
+      </c>
       <c r="L7">
         <v>0.7</v>
       </c>
       <c r="M7">
-        <v>-0.79396182298660301</v>
-      </c>
-      <c r="N7" s="2"/>
+        <v>-0.793961822986603</v>
+      </c>
       <c r="O7">
         <v>61.9581507902572</v>
       </c>
       <c r="P7">
-        <v>35.799999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>-0.78409612178802501</v>
+        <v>-0.784096121788025</v>
       </c>
       <c r="C8">
         <v>3.8080496541111</v>
       </c>
       <c r="D8">
-        <v>35.701685167780703</v>
+        <v>35.7016851677807</v>
       </c>
       <c r="E8">
-        <v>4.3411319857763901</v>
+        <v>4.34113198577639</v>
       </c>
       <c r="F8">
-        <v>3243.6701035933902</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+        <v>3243.67010359339</v>
+      </c>
       <c r="I8">
-        <v>30.140670448875401</v>
+        <v>30.1406704488754</v>
       </c>
       <c r="J8">
-        <v>3.2987484625821599</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>3.29874846258216</v>
+      </c>
       <c r="L8">
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>-0.85382533073425304</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>-0.853825330734253</v>
+      </c>
       <c r="O8">
-        <v>65.842355616656207</v>
+        <v>65.84235561665621</v>
       </c>
       <c r="P8">
         <v>33.1</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>-0.74563235044479403</v>
+        <v>-0.745632350444794</v>
       </c>
       <c r="C9">
-        <v>3.7844273824770398</v>
+        <v>3.78442738247704</v>
       </c>
       <c r="D9">
         <v>37.4824331013481</v>
@@ -798,85 +746,77 @@
         <v>1.90242859700484</v>
       </c>
       <c r="F9">
-        <v>3478.9248877067098</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+        <v>3478.92488770671</v>
+      </c>
       <c r="I9">
-        <v>31.368152344919601</v>
+        <v>31.3681523449196</v>
       </c>
       <c r="J9">
-        <v>2.2761847800212101</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>2.27618478002121</v>
+      </c>
       <c r="L9">
         <v>2.7</v>
       </c>
       <c r="M9">
         <v>-0.815987229347229</v>
       </c>
-      <c r="N9" s="2"/>
       <c r="O9">
-        <v>68.850585446267701</v>
+        <v>68.8505854462677</v>
       </c>
       <c r="P9">
         <v>29.6</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>-0.65470582246780396</v>
+        <v>-0.654705822467804</v>
       </c>
       <c r="C10">
-        <v>2.8940528865636801</v>
+        <v>2.89405288656368</v>
       </c>
       <c r="D10">
         <v>40.2763008714604</v>
       </c>
       <c r="E10">
-        <v>6.5649206822471902</v>
+        <v>6.56492068224719</v>
       </c>
       <c r="F10">
-        <v>4194.7575066198096</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+        <v>4194.75750661981</v>
+      </c>
       <c r="I10">
-        <v>34.313995493383501</v>
+        <v>34.3139954933835</v>
       </c>
       <c r="J10">
-        <v>8.4000959398746193</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>8.400095939874619</v>
+      </c>
       <c r="L10">
         <v>0.6</v>
       </c>
       <c r="M10">
-        <v>-0.72868239879608199</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>-0.728682398796082</v>
+      </c>
       <c r="O10">
-        <v>74.590296364843894</v>
+        <v>74.59029636484389</v>
       </c>
       <c r="P10">
         <v>24.9</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>-0.74457442760467496</v>
+        <v>-0.744574427604675</v>
       </c>
       <c r="C11">
-        <v>0.52092433674910199</v>
+        <v>0.520924336749102</v>
       </c>
       <c r="D11">
-        <v>29.309628834542501</v>
+        <v>29.3096288345425</v>
       </c>
       <c r="E11">
         <v>1.0910129698311</v>
@@ -884,30 +824,26 @@
       <c r="F11">
         <v>4053.36331139298</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
       <c r="I11">
-        <v>28.037717228218298</v>
+        <v>28.0377172282183</v>
       </c>
       <c r="J11">
-        <v>5.1599682918104701</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>5.15996829181047</v>
+      </c>
       <c r="L11">
         <v>-3.7</v>
       </c>
       <c r="M11">
-        <v>-0.67367577552795399</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>-0.673675775527954</v>
+      </c>
       <c r="O11">
-        <v>57.347346062760799</v>
+        <v>57.3473460627608</v>
       </c>
       <c r="P11">
         <v>19.7</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -915,313 +851,301 @@
         <v>-0.707744359970093</v>
       </c>
       <c r="C12">
-        <v>-2.3217261660452801</v>
+        <v>-2.32172616604528</v>
       </c>
       <c r="D12">
-        <v>32.485695179913499</v>
+        <v>32.4856951799135</v>
       </c>
       <c r="E12">
-        <v>4.0291378798662096</v>
+        <v>4.02913787986621</v>
       </c>
       <c r="F12">
         <v>4520.30959039763</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
       <c r="I12">
-        <v>33.291689733592698</v>
+        <v>33.2916897335927</v>
       </c>
       <c r="J12">
         <v>3.55437734567847</v>
       </c>
-      <c r="K12" s="2"/>
       <c r="L12">
         <v>-1.4</v>
       </c>
       <c r="M12">
-        <v>-0.58667445182800304</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>-0.586674451828003</v>
+      </c>
       <c r="O12">
-        <v>65.777384913506197</v>
+        <v>65.7773849135062</v>
       </c>
       <c r="P12">
-        <v>18.399999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>-0.64170813560485795</v>
+        <v>-0.641708135604858</v>
       </c>
       <c r="C13">
-        <v>-0.50658708768493199</v>
+        <v>-0.506587087684932</v>
       </c>
       <c r="D13">
-        <v>36.113369439351303</v>
+        <v>36.1133694393513</v>
       </c>
       <c r="E13">
-        <v>8.4814765633282292</v>
+        <v>8.481476563328229</v>
       </c>
       <c r="F13">
-        <v>5153.6916424375004</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+        <v>5153.6916424375</v>
+      </c>
       <c r="I13">
-        <v>33.922314313173501</v>
+        <v>33.9223143131735</v>
       </c>
       <c r="J13">
-        <v>4.4745326579583597</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>4.47453265795836</v>
+      </c>
       <c r="L13">
         <v>-0.1</v>
       </c>
       <c r="M13">
-        <v>-0.68655753135681197</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>-0.686557531356812</v>
+      </c>
       <c r="O13">
-        <v>70.035683752524903</v>
+        <v>70.0356837525249</v>
       </c>
       <c r="P13">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.50859785079956099</v>
+        <v>-0.508597850799561</v>
       </c>
       <c r="C14">
-        <v>-0.16690955649422801</v>
+        <v>-0.166909556494228</v>
       </c>
       <c r="D14">
         <v>34.8314108177156</v>
       </c>
       <c r="E14">
-        <v>5.7832123361720003</v>
+        <v>5.783212336172</v>
       </c>
       <c r="F14">
         <v>5634.08393191094</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
       <c r="I14">
         <v>32.1715182739742</v>
       </c>
       <c r="J14">
-        <v>5.1017218095866799</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>5.10172180958668</v>
+      </c>
       <c r="L14">
         <v>-2.8</v>
       </c>
       <c r="M14">
-        <v>-0.57030647993087802</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>-0.570306479930878</v>
+      </c>
       <c r="O14">
-        <v>67.002929091689793</v>
+        <v>67.00292909168979</v>
       </c>
       <c r="P14">
         <v>19.3</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>-0.50291198492050204</v>
+        <v>-0.502911984920502</v>
       </c>
       <c r="C15">
-        <v>-0.96603783242001595</v>
+        <v>-0.966037832420016</v>
       </c>
       <c r="D15">
         <v>32.3752665078284</v>
       </c>
       <c r="E15">
-        <v>7.2112365367915903</v>
+        <v>7.21123653679159</v>
       </c>
       <c r="F15">
-        <v>6109.2903151034097</v>
+        <v>6109.29031510341</v>
       </c>
       <c r="G15">
-        <v>33.530977470257596</v>
+        <v>33.5309774702576</v>
       </c>
       <c r="H15">
-        <v>30.565842337122099</v>
+        <v>30.5658423371221</v>
       </c>
       <c r="I15">
-        <v>31.058033826412998</v>
+        <v>31.058033826413</v>
       </c>
       <c r="J15">
-        <v>2.7217757771036499</v>
+        <v>2.72177577710365</v>
       </c>
       <c r="K15">
         <v>2.36439108722504</v>
       </c>
       <c r="L15">
-        <v>-7.5323622666566497</v>
+        <v>-7.53236226665665</v>
       </c>
       <c r="M15">
         <v>-0.178656712174416</v>
       </c>
       <c r="N15">
-        <v>14.123233914217501</v>
+        <v>14.1232339142175</v>
       </c>
       <c r="O15">
-        <v>63.433300334241402</v>
+        <v>63.4333003342414</v>
       </c>
       <c r="P15">
         <v>23.4</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>-0.74111849069595304</v>
+        <v>-0.741118490695953</v>
       </c>
       <c r="C16">
-        <v>-0.65104797091370403</v>
+        <v>-0.651047970913704</v>
       </c>
       <c r="D16">
-        <v>31.355036694031799</v>
+        <v>31.3550366940318</v>
       </c>
       <c r="E16">
-        <v>4.2260652038845601</v>
+        <v>4.22606520388456</v>
       </c>
       <c r="F16">
-        <v>6405.7997930044103</v>
+        <v>6405.79979300441</v>
       </c>
       <c r="G16">
-        <v>33.326879667249599</v>
+        <v>33.3268796672496</v>
       </c>
       <c r="H16">
         <v>28.8901339676781</v>
       </c>
       <c r="I16">
-        <v>30.071339927724701</v>
+        <v>30.0713399277247</v>
       </c>
       <c r="J16">
-        <v>3.5892201661666898</v>
+        <v>3.58922016616669</v>
       </c>
       <c r="K16">
-        <v>2.5285013419882998</v>
+        <v>2.5285013419883</v>
       </c>
       <c r="L16">
-        <v>-8.6924989789571399</v>
+        <v>-8.69249897895714</v>
       </c>
       <c r="M16">
-        <v>-1.85332093387842E-2</v>
+        <v>-0.0185332093387842</v>
       </c>
       <c r="N16">
         <v>14.0206757250712</v>
       </c>
       <c r="O16">
-        <v>61.426376621756503</v>
+        <v>61.4263766217565</v>
       </c>
       <c r="P16">
         <v>28.2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-0.67237687110900901</v>
+        <v>-0.672376871109009</v>
       </c>
       <c r="C17">
-        <v>-2.2848440859119199</v>
+        <v>-2.28484408591192</v>
       </c>
       <c r="D17">
         <v>22.754485726599</v>
       </c>
       <c r="E17">
-        <v>0.11969210928761199</v>
+        <v>0.119692109287612</v>
       </c>
       <c r="F17">
-        <v>5976.1596805650997</v>
+        <v>5976.1596805651</v>
       </c>
       <c r="G17">
-        <v>34.075853824724298</v>
+        <v>34.0758538247243</v>
       </c>
       <c r="H17">
-        <v>30.845883378935099</v>
+        <v>30.8458833789351</v>
       </c>
       <c r="I17">
-        <v>25.073553981183601</v>
+        <v>25.0735539811836</v>
       </c>
       <c r="J17">
-        <v>3.9666462325535301</v>
+        <v>3.96664623255353</v>
       </c>
       <c r="K17">
-        <v>3.4425616017305898</v>
+        <v>3.44256160173059</v>
       </c>
       <c r="L17">
         <v>-5.69774311670289</v>
       </c>
       <c r="M17">
-        <v>-0.14734497666358901</v>
+        <v>-0.147344976663589</v>
       </c>
       <c r="N17">
-        <v>16.389053486835898</v>
+        <v>16.3890534868359</v>
       </c>
       <c r="O17">
-        <v>47.828039707782601</v>
+        <v>47.8280397077826</v>
       </c>
       <c r="P17">
         <v>36.4</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>-0.68079274892806996</v>
+        <v>-0.68079274892807</v>
       </c>
       <c r="C18">
-        <v>0.92188082330963095</v>
+        <v>0.9218808233096309</v>
       </c>
       <c r="D18">
-        <v>20.539291155890002</v>
+        <v>20.53929115589</v>
       </c>
       <c r="E18">
-        <v>-0.68795424587794696</v>
+        <v>-0.687954245877947</v>
       </c>
       <c r="F18">
-        <v>5917.6377127148098</v>
+        <v>5917.63771271481</v>
       </c>
       <c r="G18">
         <v>35.0549572104551</v>
       </c>
       <c r="H18">
-        <v>28.641207958401299</v>
+        <v>28.6412079584013</v>
       </c>
       <c r="I18">
-        <v>19.995200643774702</v>
+        <v>19.9952006437747</v>
       </c>
       <c r="J18">
         <v>1.72826463324535</v>
       </c>
       <c r="K18">
-        <v>5.6700822817147696</v>
+        <v>5.67008228171477</v>
       </c>
       <c r="L18">
-        <v>-8.5716499573941505</v>
+        <v>-8.57164995739415</v>
       </c>
       <c r="M18">
-        <v>-9.1710433363914504E-2</v>
+        <v>-0.0917104333639145</v>
       </c>
       <c r="N18">
         <v>14.5417706457609</v>
@@ -1233,24 +1157,24 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>-0.62610465288162198</v>
+        <v>-0.626104652881622</v>
       </c>
       <c r="C19">
-        <v>-0.38839105807421898</v>
+        <v>-0.388391058074219</v>
       </c>
       <c r="D19">
-        <v>21.485587391276901</v>
+        <v>21.4855873912769</v>
       </c>
       <c r="E19">
         <v>5.97039880954841</v>
       </c>
       <c r="F19">
-        <v>6233.3224479771798</v>
+        <v>6233.32244797718</v>
       </c>
       <c r="G19">
         <v>31.5192679680287</v>
@@ -1262,33 +1186,33 @@
         <v>22.1321359260048</v>
       </c>
       <c r="J19">
-        <v>0.41733558866682002</v>
+        <v>0.41733558866682</v>
       </c>
       <c r="K19">
         <v>5.72540950394934</v>
       </c>
       <c r="L19">
-        <v>-6.3651971928587399</v>
+        <v>-6.36519719285874</v>
       </c>
       <c r="M19">
-        <v>-7.8932076692581205E-2</v>
+        <v>-0.0789320766925812</v>
       </c>
       <c r="N19">
-        <v>13.689304312677301</v>
+        <v>13.6893043126773</v>
       </c>
       <c r="O19">
-        <v>43.617723317281701</v>
+        <v>43.6177233172817</v>
       </c>
       <c r="P19">
         <v>47.4</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-0.62950038909912098</v>
+        <v>-0.629500389099121</v>
       </c>
       <c r="C20">
         <v>-1.53396782171926</v>
@@ -1297,93 +1221,93 @@
         <v>23.5438701347327</v>
       </c>
       <c r="E20">
-        <v>1.0442946067960699</v>
+        <v>1.04429460679607</v>
       </c>
       <c r="F20">
-        <v>6303.9188665833799</v>
+        <v>6303.91886658338</v>
       </c>
       <c r="G20">
-        <v>33.725044920669802</v>
+        <v>33.7250449206698</v>
       </c>
       <c r="H20">
         <v>31.2062328120813</v>
       </c>
       <c r="I20">
-        <v>24.465477480750899</v>
+        <v>24.4654774807509</v>
       </c>
       <c r="J20">
-        <v>-0.22410324600550099</v>
+        <v>-0.224103246005501</v>
       </c>
       <c r="K20">
-        <v>6.5459087962662297</v>
+        <v>6.54590879626623</v>
       </c>
       <c r="L20">
-        <v>-3.5251485056439198</v>
+        <v>-3.52514850564392</v>
       </c>
       <c r="M20">
-        <v>-9.4721168279647799E-2</v>
+        <v>-0.0947211682796478</v>
       </c>
       <c r="N20">
         <v>14.2925485653785</v>
       </c>
       <c r="O20">
-        <v>48.009347615483598</v>
+        <v>48.0093476154836</v>
       </c>
       <c r="P20">
         <v>49.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>-0.50927501916885398</v>
+        <v>-0.509275019168854</v>
       </c>
       <c r="C21">
-        <v>-0.51005410938599904</v>
+        <v>-0.510054109385999</v>
       </c>
       <c r="D21">
-        <v>24.048634598571301</v>
+        <v>24.0486345985713</v>
       </c>
       <c r="E21">
-        <v>0.16540446460030001</v>
+        <v>0.1654044646003</v>
       </c>
       <c r="F21">
-        <v>6205.0576524676599</v>
+        <v>6205.05765246766</v>
       </c>
       <c r="G21">
-        <v>33.146896495393598</v>
+        <v>33.1468964953936</v>
       </c>
       <c r="H21">
-        <v>29.659998464266302</v>
+        <v>29.6599984642663</v>
       </c>
       <c r="I21">
-        <v>24.034214894759401</v>
+        <v>24.0342148947594</v>
       </c>
       <c r="J21">
-        <v>0.26601251546614602</v>
+        <v>0.266012515466146</v>
       </c>
       <c r="K21">
-        <v>7.5031476572440701</v>
+        <v>7.50314765724407</v>
       </c>
       <c r="L21">
-        <v>-4.2703459565283302</v>
+        <v>-4.27034595652833</v>
       </c>
       <c r="M21">
-        <v>-0.23821775615215299</v>
+        <v>-0.238217756152153</v>
       </c>
       <c r="N21">
         <v>13.4008895884716</v>
       </c>
       <c r="O21">
-        <v>48.082849493330698</v>
+        <v>48.0828494933307</v>
       </c>
       <c r="P21">
         <v>52.1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -1394,220 +1318,210 @@
         <v>2.09140003785184</v>
       </c>
       <c r="D22">
-        <v>23.283562164242401</v>
+        <v>23.2835621642424</v>
       </c>
       <c r="E22">
         <v>-9.24509619165865</v>
       </c>
       <c r="F22">
-        <v>5463.6451534859798</v>
+        <v>5463.64515348598</v>
       </c>
       <c r="G22">
-        <v>34.039675416688198</v>
+        <v>34.0396754166882</v>
       </c>
       <c r="H22">
-        <v>27.121086732652401</v>
+        <v>27.1210867326524</v>
       </c>
       <c r="I22">
         <v>20.7057487735965</v>
       </c>
       <c r="J22">
-        <v>-0.33887239256218099</v>
+        <v>-0.338872392562181</v>
       </c>
       <c r="K22">
-        <v>8.1021033485421494</v>
+        <v>8.102103348542149</v>
       </c>
       <c r="L22">
-        <v>-7.4914181131671898</v>
+        <v>-7.49141811316719</v>
       </c>
       <c r="M22">
-        <v>-0.27024322748184199</v>
+        <v>-0.270243227481842</v>
       </c>
       <c r="N22">
         <v>12.9414345922817</v>
       </c>
       <c r="O22">
-        <v>43.989310937838901</v>
+        <v>43.9893109378389</v>
       </c>
       <c r="P22">
         <v>63.6</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>-0.59461385011672996</v>
+        <v>-0.59461385011673</v>
       </c>
       <c r="C23">
-        <v>2.8371683691104801</v>
+        <v>2.83716836911048</v>
       </c>
       <c r="D23">
-        <v>27.065975584002501</v>
+        <v>27.0659755840025</v>
       </c>
       <c r="E23">
-        <v>9.4218926903363105</v>
+        <v>9.42189269033631</v>
       </c>
       <c r="F23">
-        <v>6061.3235018171099</v>
+        <v>6061.32350181711</v>
       </c>
       <c r="G23">
-        <v>31.926174930312499</v>
+        <v>31.9261749303125</v>
       </c>
       <c r="H23">
-        <v>29.671482040968801</v>
+        <v>29.6714820409688</v>
       </c>
       <c r="I23">
         <v>26.1953000265705</v>
       </c>
       <c r="J23">
-        <v>0.13325138609637899</v>
+        <v>0.133251386096379</v>
       </c>
       <c r="K23">
-        <v>3.6620129774277301</v>
+        <v>3.66201297742773</v>
       </c>
       <c r="L23">
-        <v>-2.9045751242084199</v>
+        <v>-2.90457512420842</v>
       </c>
       <c r="M23">
-        <v>-0.25738736987114003</v>
+        <v>-0.25738736987114</v>
       </c>
       <c r="N23">
-        <v>12.735868406390001</v>
+        <v>12.73586840639</v>
       </c>
       <c r="O23">
-        <v>53.261275610573001</v>
+        <v>53.261275610573</v>
       </c>
       <c r="P23">
         <v>61.8</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>-0.63026487827301003</v>
+        <v>-0.63026487827301</v>
       </c>
       <c r="C24">
-        <v>1.9369711178145299</v>
+        <v>1.93697111781453</v>
       </c>
       <c r="D24">
         <v>30.9252456928287</v>
       </c>
       <c r="E24">
-        <v>5.8684235486231104</v>
+        <v>5.86842354862311</v>
       </c>
       <c r="F24">
-        <v>6515.5852841833603</v>
+        <v>6515.58528418336</v>
       </c>
       <c r="G24">
         <v>30.4365983203311</v>
       </c>
       <c r="H24">
-        <v>30.962540535543699</v>
+        <v>30.9625405355437</v>
       </c>
       <c r="I24">
-        <v>30.955547125957299</v>
+        <v>30.9555471259573</v>
       </c>
       <c r="J24">
-        <v>3.4661697221307599</v>
+        <v>3.46616972213076</v>
       </c>
       <c r="K24">
-        <v>4.7439164592724303</v>
+        <v>4.74391645927243</v>
       </c>
       <c r="L24">
-        <v>-6.2162674566409804E-3</v>
+        <v>-0.00621626745664098</v>
       </c>
       <c r="M24">
-        <v>-0.37122431397437999</v>
+        <v>-0.37122431397438</v>
       </c>
       <c r="N24">
-        <v>13.089198178420601</v>
+        <v>13.0891981784206</v>
       </c>
       <c r="O24">
-        <v>61.880792818785999</v>
+        <v>61.880792818786</v>
       </c>
       <c r="P24">
         <v>57.2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>-0.64733743667602495</v>
+        <v>-0.6473374366760249</v>
       </c>
       <c r="C25">
-        <v>1.9404024484996301</v>
+        <v>1.94040244849963</v>
       </c>
       <c r="D25">
-        <v>28.565929587542499</v>
+        <v>28.5659295875425</v>
       </c>
       <c r="E25">
-        <v>1.9882381398423501</v>
+        <v>1.98823813984235</v>
       </c>
       <c r="F25">
-        <v>6737.8474837963804</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
+        <v>6737.84748379638</v>
+      </c>
       <c r="I25">
-        <v>28.431823977366601</v>
+        <v>28.4318239773666</v>
       </c>
       <c r="J25">
-        <v>2.2156876423706202</v>
-      </c>
-      <c r="K25" s="2"/>
+        <v>2.21568764237062</v>
+      </c>
       <c r="L25">
         <v>-3.5</v>
       </c>
       <c r="M25">
-        <v>-0.33813998103141801</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>-0.338139981031418</v>
+      </c>
       <c r="O25">
-        <v>56.997753564909097</v>
+        <v>56.9977535649091</v>
       </c>
       <c r="P25">
         <v>54.3</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>5.6689912586126603</v>
+        <v>5.66899125861266</v>
       </c>
       <c r="D26">
-        <v>30.278600678466798</v>
+        <v>30.2786006784668</v>
       </c>
       <c r="E26">
-        <v>-2.0012547634102602</v>
+        <v>-2.00125476341026</v>
       </c>
       <c r="F26">
-        <v>6874.7057397660001</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+        <v>6874.705739766</v>
+      </c>
       <c r="I26">
-        <v>26.924538874658701</v>
+        <v>26.9245388746587</v>
       </c>
       <c r="J26">
         <v>1.54732515615369</v>
       </c>
-      <c r="K26" s="2"/>
       <c r="L26">
         <v>-1.3</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
       <c r="O26">
-        <v>57.203139553125503</v>
+        <v>57.2031395531255</v>
       </c>
       <c r="P26">
         <v>53.8</v>
